--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Scenarios" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Login page" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Dashboard page" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Test Scenarios" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Login page" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Dashboard page" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Dashboard page'!$A$4:$K$4</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="94">
   <si>
     <t xml:space="preserve">Project Name</t>
   </si>
@@ -86,6 +86,9 @@
     <t xml:space="preserve">SC_0001</t>
   </si>
   <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
     <t xml:space="preserve">Login</t>
   </si>
   <si>
@@ -162,6 +165,9 @@
   </si>
   <si>
     <t xml:space="preserve">SC_0009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate that, the user can reset password clicking on the “Forgot your password?” link</t>
   </si>
   <si>
     <t xml:space="preserve">SC_0010</t>
@@ -274,6 +280,30 @@
     <t xml:space="preserve">The main banner is visible</t>
   </si>
   <si>
+    <t xml:space="preserve">TC_0005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reset password with valid Username</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The browser is `MS Edge`
+2. I’m on the target URL
+3. The “Forgot your password?” link is visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Path: `web/index.php/auth/login`
+2. Username: Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. I click the “Forgot your password?” link
+2. I enter the username in the `Username` field
+3. I click `Reset Password` button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`Reset Password link sent successfully
+` notice is displayed</t>
+  </si>
+  <si>
     <t xml:space="preserve">SU_0002</t>
   </si>
   <si>
@@ -285,9 +315,6 @@
   </si>
   <si>
     <t xml:space="preserve">1. Path: `web/index.php/dashboard/index`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_0005</t>
   </si>
   <si>
     <t xml:space="preserve">TC_0006</t>
@@ -317,6 +344,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -338,6 +366,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -393,35 +422,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -439,14 +468,13 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFDDDDDD"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
+          <fgColor rgb="00FFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -526,119 +554,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.67"/>
@@ -782,19 +704,19 @@
         <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1</v>
@@ -802,22 +724,22 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>3</v>
@@ -825,22 +747,22 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>1</v>
@@ -848,118 +770,130 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -991,8 +925,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:K9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A2:K10"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="12.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13.35"/>
@@ -1001,19 +935,18 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="28.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="26.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="30.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="17.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="17.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="2" width="21.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="31.16"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1021,7 +954,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>14</v>
@@ -1030,185 +963,217 @@
         <v>15</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1230,7 +1195,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:K14"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="12.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13.35"/>
@@ -1241,16 +1206,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="30.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="17.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="17.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="31.16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1258,7 +1223,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>14</v>
@@ -1267,106 +1232,106 @@
         <v>15</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" state="visible" r:id="rId2"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="114">
   <si>
     <t xml:space="preserve">Project Name</t>
   </si>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Validate that, the login goes successful with valid credentials</t>
   </si>
   <si>
-    <t xml:space="preserve">P-00</t>
+    <t xml:space="preserve">High</t>
   </si>
   <si>
     <t xml:space="preserve">SC_0002</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">Validate that, the login goes unsuccessful with invalid credentials</t>
   </si>
   <si>
-    <t xml:space="preserve">P-05</t>
+    <t xml:space="preserve">Urgent</t>
   </si>
   <si>
     <t xml:space="preserve">SC_0003</t>
@@ -116,6 +116,9 @@
     <t xml:space="preserve">Validate that, the application banner is visible</t>
   </si>
   <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
     <t xml:space="preserve">SC_0004</t>
   </si>
   <si>
@@ -131,7 +134,7 @@
     <t xml:space="preserve">SC_0005</t>
   </si>
   <si>
-    <t xml:space="preserve">Employee Distribution by Sub Unit</t>
+    <t xml:space="preserve">Employee Distribution by Sub Unit widget</t>
   </si>
   <si>
     <t xml:space="preserve">Validate that, hovering on the pivot displays the tool-tip</t>
@@ -140,13 +143,13 @@
     <t xml:space="preserve">SC_0006</t>
   </si>
   <si>
-    <t xml:space="preserve">Employee Distribution by Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validate that, the module is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-04</t>
+    <t xml:space="preserve">All dashboard widgets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate that, all widgets is displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium</t>
   </si>
   <si>
     <t xml:space="preserve">SC_0007</t>
@@ -155,7 +158,7 @@
     <t xml:space="preserve">Profile menu</t>
   </si>
   <si>
-    <t xml:space="preserve">Validate that, the profile menu opens upon clicking the profile photo</t>
+    <t xml:space="preserve">Validate that, the profile menu opens upon clicking the profile icon</t>
   </si>
   <si>
     <t xml:space="preserve">SC_0008</t>
@@ -314,22 +317,102 @@
 2. I’m logged in and on the dashboard page</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Path: `web/index.php/dashboard/index`</t>
+    <t xml:space="preserve">1. Username: `Admin`
+2. Password: `admin123`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee Distribution by Sub Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hover on the pivot table under the `Employee Distribution by Sub Unit` module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Username: `Admin`
+2. Password: `admin123`
+3. Path: `web/index.php/dashboard/index`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. I hover the mouse on the pivot table graph items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The tool-tip for the hovered graph is displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time at Work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check if the widget is displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Check if the widget is visible on the page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The widget is visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Actions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quick Launch</t>
   </si>
   <si>
     <t xml:space="preserve">TC_0006</t>
   </si>
   <si>
+    <t xml:space="preserve">Buzz Latest Posts</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC_0007</t>
   </si>
   <si>
+    <t xml:space="preserve">Employees on Leave Today</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC_0008</t>
   </si>
   <si>
     <t xml:space="preserve">TC_0009</t>
   </si>
   <si>
+    <t xml:space="preserve">Employee Distribution by Location</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC_0010</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SC_0007
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">SC_0008</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Profile icon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open &amp; close the profile menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click the profile icon at the top-right corner
+2. Wait until the profile menu opens up
+3. Click an empty space on the page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The profile menu opens up
+2. The profile menu closes upon clicking the empty space</t>
   </si>
 </sst>
 </file>
@@ -339,7 +422,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -367,6 +450,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -417,7 +505,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -451,6 +539,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -762,7 +858,7 @@
         <v>28</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>1</v>
@@ -770,107 +866,122 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G13" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>39</v>
+        <v>29</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>19</v>
@@ -882,15 +993,18 @@
         <v>20</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>19</v>
@@ -943,10 +1057,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -954,7 +1068,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>14</v>
@@ -963,30 +1077,30 @@
         <v>15</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>18</v>
@@ -995,30 +1109,30 @@
         <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>23</v>
@@ -1027,30 +1141,30 @@
         <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>23</v>
@@ -1059,30 +1173,30 @@
         <v>20</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>23</v>
@@ -1091,30 +1205,30 @@
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>26</v>
@@ -1126,54 +1240,54 @@
         <v>28</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1194,7 +1308,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:K14"/>
+  <dimension ref="A2:K17"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="12.23"/>
@@ -1202,7 +1316,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="10.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="24.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="28.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="26.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="26.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="30.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="17.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="17.52"/>
@@ -1212,10 +1326,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1223,7 +1337,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>14</v>
@@ -1232,107 +1346,349 @@
         <v>15</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>70</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>75</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="1"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>80</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>101</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>93</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F17" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:K4"/>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" state="visible" r:id="rId2"/>
@@ -259,6 +259,9 @@
 3. Password: InvPass</t>
   </si>
   <si>
+    <t xml:space="preserve">TC_0004</t>
+  </si>
+  <si>
     <t xml:space="preserve">Login using invalid username &amp; invalid password</t>
   </si>
   <si>
@@ -267,7 +270,7 @@
 3. Password: InvPass</t>
   </si>
   <si>
-    <t xml:space="preserve">TC_0004</t>
+    <t xml:space="preserve">TC_0005</t>
   </si>
   <si>
     <t xml:space="preserve">1. The browser is `MS Edge`
@@ -283,7 +286,7 @@
     <t xml:space="preserve">The main banner is visible</t>
   </si>
   <si>
-    <t xml:space="preserve">TC_0005</t>
+    <t xml:space="preserve">TC_0006</t>
   </si>
   <si>
     <t xml:space="preserve">Reset password with valid Username</t>
@@ -356,9 +359,6 @@
     <t xml:space="preserve">Quick Launch</t>
   </si>
   <si>
-    <t xml:space="preserve">TC_0006</t>
-  </si>
-  <si>
     <t xml:space="preserve">Buzz Latest Posts</t>
   </si>
   <si>
@@ -380,24 +380,8 @@
     <t xml:space="preserve">TC_0010</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SC_0007
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">SC_0008</t>
-    </r>
+    <t xml:space="preserve">SC_0007
+SC_0008</t>
   </si>
   <si>
     <t xml:space="preserve">Profile icon</t>
@@ -422,7 +406,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -450,11 +434,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -542,7 +521,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1196,7 +1175,7 @@
     </row>
     <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>23</v>
@@ -1205,13 +1184,13 @@
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>63</v>
@@ -1228,7 +1207,7 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>26</v>
@@ -1240,19 +1219,19 @@
         <v>28</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>65</v>
@@ -1260,7 +1239,7 @@
     </row>
     <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>46</v>
@@ -1269,22 +1248,22 @@
         <v>20</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>65</v>
@@ -1329,7 +1308,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1378,13 +1357,13 @@
         <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>63</v>
@@ -1407,25 +1386,25 @@
         <v>34</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>65</v>
@@ -1439,25 +1418,25 @@
         <v>37</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>65</v>
@@ -1465,31 +1444,31 @@
     </row>
     <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>65</v>
@@ -1497,31 +1476,31 @@
     </row>
     <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>65</v>
@@ -1529,7 +1508,7 @@
     </row>
     <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>37</v>
@@ -1538,22 +1517,22 @@
         <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>65</v>
@@ -1570,22 +1549,22 @@
         <v>104</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>65</v>
@@ -1599,25 +1578,25 @@
         <v>37</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>65</v>
@@ -1634,22 +1613,22 @@
         <v>107</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>65</v>
@@ -1669,10 +1648,10 @@
         <v>111</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>112</v>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,9 +8,9 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Scenarios" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Login page" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Dashboard page" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Test Scenarios" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Login page" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Dashboard page" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Dashboard page'!$A$4:$K$4</definedName>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">All dashboard widgets</t>
   </si>
   <si>
-    <t xml:space="preserve">Validate that, all widgets is displayed</t>
+    <t xml:space="preserve">Validate that, all widgets are displayed</t>
   </si>
   <si>
     <t xml:space="preserve">Medium</t>
@@ -543,13 +543,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFDDDDDD"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -629,13 +630,119 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.67"/>
@@ -1019,7 +1126,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:K10"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="12.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13.35"/>
@@ -1288,7 +1395,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:K17"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="12.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13.35"/>
